--- a/胎壓檢測器資料庫_V10/BMW M_Data.xlsx
+++ b/胎壓檢測器資料庫_V10/BMW M_Data.xlsx
@@ -3353,7 +3353,7 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>09/2018 -</t>
+          <t>09/2018 -, 09/2018 - 12/2026</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
@@ -3405,7 +3405,7 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>09/2018 -</t>
+          <t>09/2018 -, 09/2018 - 12/2026</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
@@ -3457,7 +3457,7 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>09/2018 -</t>
+          <t>09/2018 -, 09/2018 - 12/2026</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
@@ -3509,7 +3509,7 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>09/2018 -</t>
+          <t>09/2018 -, 09/2018 - 12/2026</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
@@ -3561,7 +3561,7 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>09/2018 -</t>
+          <t>09/2018 -, 09/2018 - 12/2026</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
@@ -3613,7 +3613,7 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>09/2018 -</t>
+          <t>09/2018 -, 09/2018 - 12/2026</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
